--- a/data/nrm-github-data-fields.xlsx
+++ b/data/nrm-github-data-fields.xlsx
@@ -499,7 +499,7 @@
         <v>선택</v>
       </c>
       <c r="D9" t="str">
-        <v>비어 있으면 전체 사용자에게 표시. 값이 있으면 해당 시리얼(전화번호) 사용자만 표시</v>
+        <v>비어 있으면 전체 사용자에게 표시. 일반 값이면 해당 SerialNo 사용자만 표시. "Admin"은 관리자 전용(문의 알림 등) — versionInfoAdminBuild 또는 userList isAdmin=true 앱만 수신</v>
       </c>
     </row>
     <row r="10">
@@ -650,7 +650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -782,28 +782,42 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>replyContent</v>
+      </c>
+      <c r="B12" t="str">
+        <v>string</v>
+      </c>
+      <c r="C12" t="str">
+        <v>선택</v>
+      </c>
+      <c r="D12" t="str">
+        <v>관리자 답변 본문. 줄바꿈 포함 가능. 미답변 시 빈 문자열</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
         <v>Createddate</v>
       </c>
-      <c r="B12" t="str">
-        <v>string</v>
-      </c>
-      <c r="C12" t="str">
-        <v>필수</v>
-      </c>
-      <c r="D12" t="str">
+      <c r="B13" t="str">
+        <v>string</v>
+      </c>
+      <c r="C13" t="str">
+        <v>필수</v>
+      </c>
+      <c r="D13" t="str">
         <v>등록 시각. 형식: YYYY-MM-DD HH:mm:ss.SSS</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -947,9 +961,23 @@
         <v>마지막 앱 실행 시각. 형식: YYYY-MM-DD HH:mm:ss.SSS. 미등록 시 null</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>isAdmin</v>
+      </c>
+      <c r="B13" t="str">
+        <v>boolean</v>
+      </c>
+      <c r="C13" t="str">
+        <v>선택</v>
+      </c>
+      <c r="D13" t="str">
+        <v>true면 해당 커스텀 APK가 관리자 권한(Admin SerialNo 알람 수신 등). 기본 admin APK는 versionInfoAdminBuild로 별도 처리</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/nrm-github-data-fields.xlsx
+++ b/data/nrm-github-data-fields.xlsx
@@ -499,7 +499,7 @@
         <v>선택</v>
       </c>
       <c r="D9" t="str">
-        <v>비어 있으면 전체 사용자에게 표시. 일반 값이면 해당 SerialNo 사용자만 표시. "Admin"은 관리자 전용(문의 알림 등) — versionInfoAdminBuild 또는 userList isAdmin=true 앱만 수신</v>
+        <v>비어 있으면 SerialNo가 설정된 모든 APK 사용자에게 표시. 값이 있으면 해당 SerialNo APK만 표시. APK SerialNo가 비어 있으면 알림 수집 안 함. "Admin"은 관리자 APK(SerialNo=Admin) 전용</v>
       </c>
     </row>
     <row r="10">
@@ -817,7 +817,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -961,23 +961,9 @@
         <v>마지막 앱 실행 시각. 형식: YYYY-MM-DD HH:mm:ss.SSS. 미등록 시 null</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>isAdmin</v>
-      </c>
-      <c r="B13" t="str">
-        <v>boolean</v>
-      </c>
-      <c r="C13" t="str">
-        <v>선택</v>
-      </c>
-      <c r="D13" t="str">
-        <v>true면 해당 커스텀 APK가 관리자 권한(Admin SerialNo 알람 수신 등). 기본 admin APK는 versionInfoAdminBuild로 별도 처리</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/nrm-github-data-fields.xlsx
+++ b/data/nrm-github-data-fields.xlsx
@@ -7,6 +7,7 @@
     <sheet name="userBanList" sheetId="2" r:id="rId2"/>
     <sheet name="inquiry" sheetId="3" r:id="rId3"/>
     <sheet name="userList" sheetId="4" r:id="rId4"/>
+    <sheet name="apkVersion" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -966,4 +967,73 @@
     <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>JSON 루트 키</v>
+      </c>
+      <c r="B1" t="str">
+        <v>(루트 객체)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>용도</v>
+      </c>
+      <c r="B2" t="str">
+        <v>GitHub Releases 공개 APK 최신 버전 (data/apkVersion.json). 앱 시작 시 PAT 없이 조회</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>필드명</v>
+      </c>
+      <c r="B4" t="str">
+        <v>타입</v>
+      </c>
+      <c r="C4" t="str">
+        <v>필수 여부</v>
+      </c>
+      <c r="D4" t="str">
+        <v>설명</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>version</v>
+      </c>
+      <c r="B5" t="str">
+        <v>string</v>
+      </c>
+      <c r="C5" t="str">
+        <v>필수</v>
+      </c>
+      <c r="D5" t="str">
+        <v>최신 릴리스 APK semver (package.json versionName과 동기화)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>createdDate</v>
+      </c>
+      <c r="B6" t="str">
+        <v>string (YYYY-MM-DD HH:mm:ss.SSS)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>필수</v>
+      </c>
+      <c r="D6" t="str">
+        <v>해당 버전 APK 빌드·등록 시각</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/data/nrm-github-data-fields.xlsx
+++ b/data/nrm-github-data-fields.xlsx
@@ -875,7 +875,7 @@
         <v>필수</v>
       </c>
       <c r="D6" t="str">
-        <v>커스텀 APK displayName (앱 설치명)</v>
+        <v>커스텀 APK legacy 기록명 (앱 상호/브랜딩과 무관, user_list 전용)</v>
       </c>
     </row>
     <row r="7">

--- a/data/nrm-github-data-fields.xlsx
+++ b/data/nrm-github-data-fields.xlsx
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -541,7 +541,7 @@
         <v>용도</v>
       </c>
       <c r="B2" t="str">
-        <v>사용자 차단·해제 이력 (data/userBanList.json). SerialNo별 최신 id 기록의 isBanned가 적용됨</v>
+        <v>기기 단위 사용자 차단·해제 이력 (data/userBanList.json). deviceId별 최신 id 기록의 isBanned가 적용됨. 로그인 계정(Google/Kakao)과 무관</v>
       </c>
     </row>
     <row r="4">
@@ -569,7 +569,7 @@
         <v>필수</v>
       </c>
       <c r="D5" t="str">
-        <v>기록 고유 ID</v>
+        <v>기록 고유 ID. 같은 deviceId는 최신 id가 적용됨</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +583,7 @@
         <v>필수</v>
       </c>
       <c r="D6" t="str">
-        <v>사용자 이름 (관리자 표시용)</v>
+        <v>차단 등록 시점의 사용자 이름 스냅샷 (관리자 표시용)</v>
       </c>
     </row>
     <row r="7">
@@ -597,54 +597,68 @@
         <v>필수</v>
       </c>
       <c r="D7" t="str">
-        <v>차단 대상 기기 시리얼(전화번호). APK NrmBrand.SERIAL_NO와 매칭</v>
+        <v>차단 등록 시점의 계정 UUID 스냅샷. 판정 키가 아님</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>content</v>
+        <v>deviceId</v>
       </c>
       <c r="B8" t="str">
         <v>string</v>
       </c>
       <c r="C8" t="str">
-        <v>선택</v>
+        <v>필수</v>
       </c>
       <c r="D8" t="str">
-        <v>차단·해제 사유 메모</v>
+        <v>차단 대상 기기. nrm_user_list.deviceId(ANDROID_ID SHA-256)와 동일. 앱 이용 차단 판정 키</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>isBanned</v>
+        <v>content</v>
       </c>
       <c r="B9" t="str">
-        <v>boolean</v>
+        <v>string</v>
       </c>
       <c r="C9" t="str">
-        <v>필수</v>
+        <v>선택</v>
       </c>
       <c r="D9" t="str">
-        <v>true면 해당 SerialNo 사용자 앱 이용 차단</v>
+        <v>차단·해제 사유 메모</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>isBanned</v>
+      </c>
+      <c r="B10" t="str">
+        <v>boolean</v>
+      </c>
+      <c r="C10" t="str">
+        <v>필수</v>
+      </c>
+      <c r="D10" t="str">
+        <v>true면 해당 deviceId 기기에서 앱 이용 차단</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>date</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B11" t="str">
         <v>string (YYYY-MM-DD)</v>
       </c>
-      <c r="C10" t="str">
-        <v>필수</v>
-      </c>
-      <c r="D10" t="str">
+      <c r="C11" t="str">
+        <v>필수</v>
+      </c>
+      <c r="D11" t="str">
         <v>기록 등록일</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -818,7 +832,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -833,7 +847,7 @@
         <v>용도</v>
       </c>
       <c r="B2" t="str">
-        <v>커스텀 APK 빌드 등록 이력 (data/custom-apk/userList.json)</v>
+        <v>OAuth 로그인 사용자 등록 이력 (data/custom-apk/userList.json). 앱이 nrm_user_list에 upsert하며 빌드 스크립트는 행을 만들지 않음</v>
       </c>
     </row>
     <row r="4">
@@ -866,7 +880,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>appName</v>
+        <v>appKind</v>
       </c>
       <c r="B6" t="str">
         <v>string</v>
@@ -875,7 +889,7 @@
         <v>필수</v>
       </c>
       <c r="D6" t="str">
-        <v>커스텀 APK legacy 기록명 (앱 상호/브랜딩과 무관, user_list 전용)</v>
+        <v>로그인 플랫폼 google | kakao</v>
       </c>
     </row>
     <row r="7">
@@ -889,12 +903,12 @@
         <v>필수</v>
       </c>
       <c r="D7" t="str">
-        <v>수신자 이름</v>
+        <v>OAuth에서 받은 표시 이름</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SerialNo</v>
+        <v>userEmail</v>
       </c>
       <c r="B8" t="str">
         <v>string</v>
@@ -903,12 +917,12 @@
         <v>필수</v>
       </c>
       <c r="D8" t="str">
-        <v>커스텀 APK에 내장된 시리얼</v>
+        <v>OAuth에서 받은 이메일</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>version</v>
+        <v>SerialNo</v>
       </c>
       <c r="B9" t="str">
         <v>string</v>
@@ -917,54 +931,82 @@
         <v>필수</v>
       </c>
       <c r="D9" t="str">
-        <v>빌드 시점 APK 버전</v>
+        <v>로그인 시 발급하는 UUID</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Createddate</v>
+        <v>isAdmin</v>
       </c>
       <c r="B10" t="str">
-        <v>string (YYYY-MM-DD)</v>
+        <v>string</v>
       </c>
       <c r="C10" t="str">
         <v>필수</v>
       </c>
       <c r="D10" t="str">
-        <v>userList 등록일</v>
+        <v>관리자 여부 y/n. 기본 n</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>deviceId</v>
+        <v>version</v>
       </c>
       <c r="B11" t="str">
-        <v>string | null</v>
+        <v>string</v>
       </c>
       <c r="C11" t="str">
-        <v>선택</v>
+        <v>필수</v>
       </c>
       <c r="D11" t="str">
-        <v>최초 설치 기기의 ANDROID_ID SHA-256 해시값. 미등록(최초 설치 전) 시 null</v>
+        <v>등록 시점 앱 버전</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>Createddate</v>
+      </c>
+      <c r="B12" t="str">
+        <v>string (YYYY-MM-DD)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>필수</v>
+      </c>
+      <c r="D12" t="str">
+        <v>userList 등록일</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>deviceId</v>
+      </c>
+      <c r="B13" t="str">
+        <v>string | null</v>
+      </c>
+      <c r="C13" t="str">
+        <v>선택</v>
+      </c>
+      <c r="D13" t="str">
+        <v>최초 설치 기기의 ANDROID_ID SHA-256 해시값. 미등록(최초 설치 전) 시 null</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
         <v>lastAccessDate</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B14" t="str">
         <v>string | null</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C14" t="str">
         <v>선택</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D14" t="str">
         <v>마지막 앱 실행 시각. 형식: YYYY-MM-DD HH:mm:ss.SSS. 미등록 시 null</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/nrm-github-data-fields.xlsx
+++ b/data/nrm-github-data-fields.xlsx
@@ -832,7 +832,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -903,26 +903,26 @@
         <v>필수</v>
       </c>
       <c r="D7" t="str">
-        <v>OAuth에서 받은 표시 이름</v>
+        <v>OAuth에서 받은 원본 표시 이름</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>userEmail</v>
+        <v>userCustomName</v>
       </c>
       <c r="B8" t="str">
-        <v>string</v>
+        <v>string | null</v>
       </c>
       <c r="C8" t="str">
-        <v>필수</v>
+        <v>선택</v>
       </c>
       <c r="D8" t="str">
-        <v>OAuth에서 받은 이메일</v>
+        <v>앱 설정에서 사용자가 지정한 계정별 표시 이름. null이면 userName 사용</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SerialNo</v>
+        <v>userEmail</v>
       </c>
       <c r="B9" t="str">
         <v>string</v>
@@ -931,12 +931,12 @@
         <v>필수</v>
       </c>
       <c r="D9" t="str">
-        <v>로그인 시 발급하는 UUID</v>
+        <v>OAuth에서 받은 이메일</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>isAdmin</v>
+        <v>oauthUserId</v>
       </c>
       <c r="B10" t="str">
         <v>string</v>
@@ -945,12 +945,12 @@
         <v>필수</v>
       </c>
       <c r="D10" t="str">
-        <v>관리자 여부 y/n. 기본 n</v>
+        <v>OAuth 공급자가 발급한 사용자 고유 ID. 이메일 미제공 계정 식별에도 사용</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>version</v>
+        <v>SerialNo</v>
       </c>
       <c r="B11" t="str">
         <v>string</v>
@@ -959,54 +959,82 @@
         <v>필수</v>
       </c>
       <c r="D11" t="str">
-        <v>등록 시점 앱 버전</v>
+        <v>로그인 시 발급하는 UUID</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Createddate</v>
+        <v>isAdmin</v>
       </c>
       <c r="B12" t="str">
-        <v>string (YYYY-MM-DD)</v>
+        <v>string</v>
       </c>
       <c r="C12" t="str">
         <v>필수</v>
       </c>
       <c r="D12" t="str">
-        <v>userList 등록일</v>
+        <v>관리자 여부 y/n. 기본 n</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>deviceId</v>
+        <v>version</v>
       </c>
       <c r="B13" t="str">
-        <v>string | null</v>
+        <v>string</v>
       </c>
       <c r="C13" t="str">
-        <v>선택</v>
+        <v>필수</v>
       </c>
       <c r="D13" t="str">
-        <v>최초 설치 기기의 ANDROID_ID SHA-256 해시값. 미등록(최초 설치 전) 시 null</v>
+        <v>등록 시점 앱 버전</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>Createddate</v>
+      </c>
+      <c r="B14" t="str">
+        <v>string (YYYY-MM-DD)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>필수</v>
+      </c>
+      <c r="D14" t="str">
+        <v>userList 등록일</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>deviceId</v>
+      </c>
+      <c r="B15" t="str">
+        <v>string | null</v>
+      </c>
+      <c r="C15" t="str">
+        <v>선택</v>
+      </c>
+      <c r="D15" t="str">
+        <v>최초 설치 기기의 ANDROID_ID SHA-256 해시값. 미등록(최초 설치 전) 시 null</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
         <v>lastAccessDate</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B16" t="str">
         <v>string | null</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C16" t="str">
         <v>선택</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D16" t="str">
         <v>마지막 앱 실행 시각. 형식: YYYY-MM-DD HH:mm:ss.SSS. 미등록 시 null</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D16"/>
   </ignoredErrors>
 </worksheet>
 </file>
